--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484191_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484191_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0353</v>
+        <v>5.6552</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9613</v>
+        <v>6.5532</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.926</v>
+        <v>-0.898</v>
       </c>
       <c r="G2" t="n">
         <v>4.5693</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4155</v>
+        <v>0.0354</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2099</v>
+        <v>-0.1982</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2056</v>
+        <v>0.2336</v>
       </c>
       <c r="V2" t="n">
         <v>3.2328</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0397</v>
+        <v>2.1902</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0016</v>
+        <v>2.8996</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9619</v>
+        <v>-0.7094</v>
       </c>
       <c r="G3" t="n">
         <v>1.0236</v>
@@ -688,13 +688,13 @@
         <v>0.3968</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4665</v>
+        <v>-0.316</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1303</v>
+        <v>-0.2323</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3362</v>
+        <v>-0.0837</v>
       </c>
       <c r="V3" t="n">
         <v>1.0858</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0294</v>
+        <v>1.9529</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4528</v>
+        <v>1.6569</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5766</v>
+        <v>0.2961</v>
       </c>
       <c r="G4" t="n">
         <v>2.7016</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4025</v>
+        <v>-0.479</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4024</v>
+        <v>-0.1983</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0001</v>
+        <v>-0.2807</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0713</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1053</v>
+        <v>0.8554</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2802</v>
+        <v>0.268</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3855</v>
+        <v>0.5874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765</v>
+        <v>1.6463</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1367</v>
+        <v>0.7653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.881</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5687</v>
+        <v>0.8517</v>
       </c>
       <c r="K5" t="n">
-        <v>0.434</v>
+        <v>0.8065</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1347</v>
+        <v>0.0453</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8037</v>
+        <v>0.7946</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5707</v>
+        <v>-0.0412</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2331</v>
+        <v>0.8357</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.1741</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6334</v>
+        <v>-1.2654</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6463</v>
+        <v>-0.5837</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9871</v>
+        <v>-0.6817</v>
       </c>
       <c r="V5" t="n">
-        <v>1.881</v>
+        <v>-0.1206</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4085</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5396</v>
+        <v>0.6238</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1093</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6489</v>
+        <v>0.7331</v>
       </c>
       <c r="G6" t="n">
         <v>2.0026</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7488</v>
+        <v>-0.6646</v>
       </c>
       <c r="T6" t="n">
         <v>-0.4364</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3124</v>
+        <v>-0.2282</v>
       </c>
       <c r="V6" t="n">
         <v>0.6745</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3427</v>
+        <v>-0.0323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0639</v>
+        <v>-0.6883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2788</v>
+        <v>0.656</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6463</v>
+        <v>0.765</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7653</v>
+        <v>-0.1367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.881</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8517</v>
+        <v>1.5687</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8065</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0453</v>
+        <v>1.1347</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7946</v>
+        <v>-0.8037</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0412</v>
+        <v>-0.5707</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8357</v>
+        <v>-0.2331</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7781</v>
+        <v>0.4959</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.2382</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9903</v>
+        <v>0.2577</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1206</v>
+        <v>1.881</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1206</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7432</v>
+        <v>-1.8684</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4456</v>
+        <v>-0.9355</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2976</v>
+        <v>-0.9329</v>
       </c>
       <c r="G8" t="n">
         <v>0.1934</v>
@@ -1078,13 +1078,13 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4686</v>
+        <v>-0.5938</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7991</v>
+        <v>-0.289</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6695</v>
+        <v>-0.3048</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1129</v>
+        <v>-3.169</v>
       </c>
       <c r="E9" t="n">
         <v>-2.3574</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.8116</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0139</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4104</v>
+        <v>0.3542</v>
       </c>
       <c r="T9" t="n">
         <v>0.2041</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2062</v>
+        <v>0.1501</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1206</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3917</v>
+        <v>-3.4198</v>
       </c>
       <c r="E10" t="n">
         <v>-2.731</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6607</v>
+        <v>-0.6888</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7761</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6479</v>
+        <v>-0.676</v>
       </c>
       <c r="T10" t="n">
         <v>-0.3004</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3475</v>
+        <v>-0.3756</v>
       </c>
       <c r="V10" t="n">
         <v>1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0037</v>
+        <v>-3.9476</v>
       </c>
       <c r="E11" t="n">
         <v>-2.0465</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9573</v>
+        <v>-1.9011</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5808</v>
@@ -1312,13 +1312,13 @@
         <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8298</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>-0.187</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6428</v>
+        <v>-0.5867</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9899</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.159500000000002</v>
+        <v>-1.159599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.509600000000001</v>
+        <v>2.5097</v>
       </c>
       <c r="F12" t="n">
         <v>-3.6692</v>
@@ -1357,7 +1357,7 @@
         <v>7.531000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.129900000000001</v>
+        <v>4.129899999999999</v>
       </c>
       <c r="I12" t="n">
         <v>3.401</v>
@@ -1366,7 +1366,7 @@
         <v>13.1241</v>
       </c>
       <c r="K12" t="n">
-        <v>8.622800000000003</v>
+        <v>8.6228</v>
       </c>
       <c r="L12" t="n">
         <v>4.5013</v>
@@ -1390,13 +1390,13 @@
         <v>5.9516</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.8829</v>
+        <v>-3.883000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9831</v>
+        <v>-1.983</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8999</v>
+        <v>-1.9</v>
       </c>
       <c r="V12" t="n">
         <v>6.1037</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9204</v>
+        <v>4.3948</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0035</v>
+        <v>2.9015</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9169</v>
+        <v>1.4933</v>
       </c>
       <c r="G13" t="n">
         <v>1.7048</v>
@@ -1468,13 +1468,13 @@
         <v>2.579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.22</v>
+        <v>0.6944</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3969</v>
+        <v>0.2949</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.177</v>
+        <v>0.3995</v>
       </c>
       <c r="V13" t="n">
         <v>0.4085</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.174</v>
+        <v>2.4411</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0588</v>
+        <v>1.4466</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1152</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.0884</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3876</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5557</v>
+        <v>-0.0565</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8319</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.881</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,75 +1579,71 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4523</v>
+        <v>1.7833</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3953</v>
+        <v>1.8502</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.0668</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.395</v>
+        <v>-0.7173</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1916</v>
+        <v>0.9126</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2034</v>
+        <v>-1.6299</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9984</v>
+        <v>1.463</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2755</v>
+        <v>2.1732</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7229</v>
+        <v>-0.7101</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3934</v>
+        <v>-2.1804</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4671</v>
+        <v>-1.2606</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9263</v>
+        <v>-0.9198</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6409</v>
+        <v>1.1833</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3808</v>
+        <v>0.2439</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2601</v>
+        <v>0.9394</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1352</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>E. MAÑES CARRETERO</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1657,73 +1653,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.223</v>
+        <v>1.5482</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6461</v>
+        <v>0.5246</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4231</v>
+        <v>1.0236</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7173</v>
+        <v>-0.0389</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9126</v>
+        <v>-0.0157</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6299</v>
+        <v>-0.0232</v>
       </c>
       <c r="J16" t="n">
-        <v>1.463</v>
+        <v>0.3827</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1732</v>
+        <v>0.3024</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7101</v>
+        <v>0.0803</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1804</v>
+        <v>-0.4216</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2606</v>
+        <v>-0.3181</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9198</v>
+        <v>-0.1035</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>0.623</v>
+        <v>0.3968</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0398</v>
+        <v>0.1418</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1352</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,71 +1731,75 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3015</v>
+        <v>1.5482</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0415</v>
+        <v>0.5246</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.74</v>
+        <v>1.0236</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1596</v>
+        <v>-0.0389</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5718</v>
+        <v>-0.0157</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4122</v>
+        <v>-0.0232</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2685</v>
+        <v>0.3827</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9816</v>
+        <v>0.3024</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2501</v>
+        <v>0.0803</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4281</v>
+        <v>-0.4216</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.3181</v>
       </c>
       <c r="O17" t="n">
-        <v>0.162</v>
+        <v>-0.1035</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2567</v>
+        <v>0.3968</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1605</v>
+        <v>0.255</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A. CRUZ URBANEJA</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1809,73 +1809,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2032</v>
+        <v>1.2342</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3937</v>
+        <v>1.4496</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1905</v>
+        <v>-0.2154</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0389</v>
+        <v>-0.1596</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0157</v>
+        <v>-1.5718</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0232</v>
+        <v>1.4122</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3827</v>
+        <v>0.2685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3024</v>
+        <v>-0.9816</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>1.2501</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4216</v>
+        <v>-0.4281</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3181</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1035</v>
+        <v>0.162</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3546</v>
+        <v>0.676</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7764</v>
+        <v>0.3119</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5782</v>
+        <v>0.3641</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1887,58 +1887,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2032</v>
+        <v>0.2356</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3937</v>
+        <v>0.9669</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1905</v>
+        <v>-0.7313</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0389</v>
+        <v>-0.395</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0157</v>
+        <v>-0.1916</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0232</v>
+        <v>-0.2034</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3827</v>
+        <v>1.9984</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3024</v>
+        <v>1.2755</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0803</v>
+        <v>0.7229</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4216</v>
+        <v>-2.3934</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3181</v>
+        <v>-1.4671</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1035</v>
+        <v>-0.9263</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3546</v>
+        <v>1.4242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7764</v>
+        <v>0.9523</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5782</v>
+        <v>0.4718</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5841</v>
+        <v>-0.7983</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9183</v>
+        <v>-1.0203</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3342</v>
+        <v>0.2219</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0486</v>
@@ -2010,13 +2010,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.6632</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3288</v>
+        <v>0.2268</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5486</v>
+        <v>0.4364</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,64 +2043,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8675</v>
+        <v>-1.059</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9585</v>
+        <v>-1.7757</v>
       </c>
       <c r="F21" t="n">
-        <v>1.091</v>
+        <v>0.7166</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9642</v>
+        <v>-1.1724</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9642</v>
+        <v>0.4134</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9642</v>
+        <v>-0.7101</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9642</v>
+        <v>0.6101</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.3202</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.4623</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.1967</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.2656</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7712</v>
+        <v>0.1134</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6802</v>
+        <v>-0.0737</v>
       </c>
       <c r="U21" t="n">
-        <v>1.091</v>
+        <v>0.187</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2733</v>
+        <v>-1.4452</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8777</v>
+        <v>0.8292</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6044</v>
+        <v>-2.2743</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1724</v>
+        <v>-0.8177</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4134</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5858</v>
+        <v>0.0789</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7101</v>
+        <v>1.0954</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6101</v>
+        <v>0.6409</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3202</v>
+        <v>0.4545</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4623</v>
+        <v>-1.9132</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1967</v>
+        <v>-1.5376</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2656</v>
+        <v>-0.3756</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1009</v>
+        <v>-0.3967</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1757</v>
+        <v>-0.2663</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.1304</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7239</v>
+        <v>-1.7432</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0891</v>
+        <v>-2.3666</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6348</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8177</v>
+        <v>-1.9642</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-1.9642</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0954</v>
+        <v>-1.9642</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6409</v>
+        <v>-1.9642</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4545</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9132</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5376</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3756</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1822</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1822</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6755</v>
+        <v>0.8955</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1846</v>
+        <v>0.2721</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4909</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4129</v>
+        <v>-0.6745</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2277,10 +2277,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2598</v>
+        <v>-3.0557</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2387</v>
+        <v>-1.0347</v>
       </c>
       <c r="F24" t="n">
         <v>-2.021</v>
@@ -2322,10 +2322,10 @@
         <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2355,19 +2355,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9562000000000013</v>
+        <v>5.084000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.275500000000001</v>
+        <v>4.2959</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3192</v>
+        <v>0.7881999999999998</v>
       </c>
       <c r="G25" t="n">
         <v>-7.569800000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.1457</v>
+        <v>-4.145700000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-3.4241</v>
@@ -2376,7 +2376,7 @@
         <v>5.9756</v>
       </c>
       <c r="K25" t="n">
-        <v>4.795</v>
+        <v>4.795000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>1.1806</v>
@@ -2385,7 +2385,7 @@
         <v>-13.5455</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.940800000000001</v>
+        <v>-8.940799999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-4.6048</v>
@@ -2400,13 +2400,13 @@
         <v>18.053</v>
       </c>
       <c r="S25" t="n">
-        <v>2.528499999999999</v>
+        <v>6.6563</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1235</v>
+        <v>2.1437</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4048</v>
+        <v>4.5125</v>
       </c>
       <c r="V25" t="n">
         <v>-6.103600000000001</v>
